--- a/output/第10期計画_代表KPIの振替案と確認事項の精査.xlsx
+++ b/output/第10期計画_代表KPIの振替案と確認事項の精査.xlsx
@@ -1079,7 +1079,7 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>★振替を要する（02シート）</t>
+          <t>振替を要する（02シート）</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>★振替を要する（02シート）</t>
+          <t>振替を要する（02シート）</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>★振替を要する（02シート）</t>
+          <t>振替を要する（02シート）</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>★振替を要する（02シート）</t>
+          <t>振替を要する（02シート）</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>★新規の提案である。測るものが「事業所側の受入れ可否」から「必要と判断されたが区域内で提供できないこと」に変わる。母集団が「在宅生活の維持が難しい利用者」の抽出であるため、区域内の在宅利用者全体の未充足率ではない。町別は東川町33.3％（12票中4）・美瑛町18.8％（69票中13）・東神楽町17.6％（17票中3）</t>
+          <t>新規の提案である。測るものが「事業所側の受入れ可否」から「必要と判断されたが区域内で提供できないこと」に変わる。母集団が「在宅生活の維持が難しい利用者」の抽出であるため、区域内の在宅利用者全体の未充足率ではない。町別は東川町33.3％（12票中4）・美瑛町18.8％（69票中13）・東神楽町17.6％（17票中3）</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_代表KPIの振替案と確認事項の精査.xlsx
+++ b/output/第10期計画_代表KPIの振替案と確認事項の精査.xlsx
@@ -1925,7 +1925,7 @@
       <c r="D15" s="13" t="n"/>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>削除しない。20.4％は第6章第4節の整備方針の根拠になる</t>
+          <t>削除しない。20.4％は代理指標であり、第6章第4節の整備方針を検討する参考情報の一つとして用いる</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
